--- a/public/downloads/milestone-tracker-template.xlsx
+++ b/public/downloads/milestone-tracker-template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">Milestone Tracker Template</t>
   </si>
@@ -94,12 +94,6 @@
     <t xml:space="preserve">Example: Project charter approved</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-01-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-09</t>
-  </si>
-  <si>
     <t xml:space="preserve">M. Nowak</t>
   </si>
   <si>
@@ -107,6 +101,15 @@
   </si>
   <si>
     <t xml:space="preserve">PHASE 2: PLANNING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: Requirements sign-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J. Alvarez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaiting stakeholder sign-off</t>
   </si>
   <si>
     <t xml:space="preserve">PHASE 3: EXECUTION</t>
@@ -879,7 +882,7 @@
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
         <f aca="false">COUNTIF(E15:E33,"Completed On Time")+COUNTIF(E15:E33,"Completed Late")+COUNTIF(E15:E33,"Delayed")+COUNTIF(E15:E33,"Upcoming")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">COUNTIF(E15:E33,"Completed On Time")</f>
@@ -891,7 +894,7 @@
       </c>
       <c r="D10" s="7" t="n">
         <f aca="false">COUNTIF(E15:E33,"Delayed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
         <f aca="false">COUNTIF(E15:E33,"Upcoming")</f>
@@ -947,11 +950,11 @@
       <c r="A15" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>25</v>
+      <c r="B15" s="11" t="n">
+        <v>45667</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>45666</v>
       </c>
       <c r="D15" s="12" t="n">
         <f aca="false">IF(OR(B15="",C15=""),"",C15-B15)</f>
@@ -962,10 +965,10 @@
         <v>Completed On Time</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1000,7 +1003,7 @@
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -1010,19 +1013,27 @@
       <c r="G19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16" t="str">
+      <c r="A20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12" t="str">
         <f aca="false">IF(OR(B20="",C20=""),"",C20-B20)</f>
         <v/>
       </c>
-      <c r="E20" s="17" t="str">
+      <c r="E20" s="13" t="str">
         <f aca="true">IF(B20="","",IF(C20&lt;&gt;"",IF(C20&lt;=B20,"Completed On Time","Completed Late"),IF(B20&lt;TODAY(),"Delayed","Upcoming")))</f>
-        <v/>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
+        <v>Delayed</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14"/>
@@ -1056,7 +1067,7 @@
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1127,7 +1138,7 @@
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -1183,36 +1194,36 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19"/>
       <c r="B37" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21"/>
       <c r="B38" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22"/>
       <c r="B39" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23"/>
       <c r="B40" s="20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B42" s="24"/>
       <c r="C42" s="24"/>
